--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3749" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -710,6 +710,22 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -2443,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP97"/>
+  <dimension ref="A1:AP98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.3203125" customWidth="true" bestFit="true"/>
@@ -5167,7 +5183,7 @@
         <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5253,46 +5269,44 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5340,7 +5354,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5364,7 +5378,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5382,7 +5396,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5395,23 +5409,25 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5460,7 +5476,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5472,22 +5488,22 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5495,14 +5511,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5521,17 +5537,17 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5580,7 +5596,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5595,19 +5611,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5615,14 +5631,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5641,18 +5657,18 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5700,7 +5716,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5715,16 +5731,16 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5735,46 +5751,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>262</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5798,11 +5812,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5820,13 +5836,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5835,19 +5851,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5855,10 +5871,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5869,31 +5885,31 @@
         <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>271</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5918,35 +5934,35 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5955,19 +5971,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5975,14 +5991,12 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5991,7 +6005,7 @@
         <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>94</v>
@@ -6003,19 +6017,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6043,28 +6057,26 @@
         <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6088,10 +6100,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -6099,24 +6111,26 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -6125,16 +6139,20 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6158,13 +6176,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6182,19 +6200,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6206,10 +6224,10 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>284</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6217,21 +6235,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6243,17 +6261,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6290,31 +6306,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6337,46 +6353,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6412,19 +6426,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6436,7 +6450,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6445,10 +6459,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6459,10 +6473,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6470,31 +6484,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6542,19 +6560,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>110</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6563,10 +6581,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6577,21 +6595,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6603,17 +6621,15 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6650,31 +6666,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6697,52 +6713,50 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>115</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6772,31 +6786,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>121</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6805,10 +6819,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>309</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6819,10 +6833,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6830,13 +6844,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6845,24 +6859,26 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6904,7 +6920,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6925,10 +6941,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6939,10 +6955,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6950,13 +6966,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6965,24 +6981,24 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>82</v>
@@ -7024,7 +7040,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7045,10 +7061,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7059,10 +7075,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7070,13 +7086,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7085,27 +7101,27 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -7144,7 +7160,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7165,10 +7181,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7179,10 +7195,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7205,19 +7221,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7227,7 +7241,7 @@
         <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>82</v>
@@ -7266,7 +7280,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7287,10 +7301,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7301,10 +7315,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7327,19 +7341,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7388,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7409,10 +7423,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7423,24 +7437,24 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7449,19 +7463,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7486,13 +7500,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7510,10 +7524,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7525,62 +7539,66 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7604,13 +7622,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7628,10 +7646,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7640,44 +7658,44 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>370</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7689,17 +7707,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7736,31 +7752,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7783,18 +7799,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7806,23 +7822,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>289</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7858,9 +7872,11 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7868,7 +7884,7 @@
         <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7880,7 +7896,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7889,10 +7905,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7903,14 +7919,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7919,7 +7933,7 @@
         <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7934,16 +7948,16 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7980,19 +7994,17 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8013,10 +8025,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8027,18 +8039,20 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="C47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8050,19 +8064,23 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8110,19 +8128,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>110</v>
+        <v>298</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8131,10 +8149,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8145,21 +8163,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8171,17 +8189,15 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8218,31 +8234,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8265,21 +8281,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8288,29 +8304,27 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>302</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>303</v>
+        <v>116</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8340,31 +8354,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>307</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8373,10 +8387,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>309</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8387,10 +8401,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8398,7 +8412,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8413,24 +8427,26 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8472,7 +8488,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8493,10 +8509,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8507,10 +8523,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8518,7 +8534,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8533,24 +8549,24 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8592,7 +8608,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8613,10 +8629,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8627,10 +8643,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8638,7 +8654,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8653,24 +8669,24 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8712,7 +8728,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8733,10 +8749,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8747,10 +8763,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8773,19 +8789,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>337</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8834,7 +8848,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8855,10 +8869,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8869,10 +8883,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8895,19 +8909,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8956,7 +8970,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8977,10 +8991,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8991,10 +9005,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9002,13 +9016,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9017,19 +9031,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>392</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>395</v>
+        <v>354</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9078,7 +9092,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9093,19 +9107,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9113,10 +9127,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9124,13 +9138,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9139,18 +9153,20 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9198,13 +9214,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9213,19 +9229,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9233,21 +9249,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9259,20 +9275,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9320,13 +9334,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9335,19 +9349,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9355,24 +9369,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9381,19 +9395,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9442,7 +9456,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9451,25 +9465,25 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9477,24 +9491,24 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9503,18 +9517,20 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>425</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9562,7 +9578,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9571,25 +9587,25 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>431</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9597,10 +9613,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9611,7 +9627,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9623,18 +9639,18 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>442</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9682,13 +9698,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9697,19 +9713,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9717,10 +9733,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9731,10 +9747,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9743,19 +9759,17 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9792,59 +9806,59 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC61" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9865,19 +9879,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9914,19 +9928,17 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9935,7 +9947,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9944,29 +9956,31 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9978,25 +9992,29 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>453</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>108</v>
+        <v>454</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10044,7 +10062,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>452</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10053,47 +10071,47 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>111</v>
+        <v>462</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10105,17 +10123,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10152,31 +10168,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10199,46 +10215,44 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>467</v>
+        <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>115</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
+        <v>116</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10274,31 +10288,31 @@
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>472</v>
+        <v>121</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10307,10 +10321,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>474</v>
+        <v>111</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10321,10 +10335,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10332,83 +10346,83 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>472</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q66" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="R66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10429,10 +10443,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10443,10 +10457,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10454,37 +10468,39 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10504,13 +10520,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10528,7 +10544,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10549,10 +10565,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10563,10 +10579,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10589,24 +10605,24 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -10648,7 +10664,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10657,7 +10673,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10669,10 +10685,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10683,10 +10699,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10709,26 +10725,24 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10770,7 +10784,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10779,7 +10793,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10791,10 +10805,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10805,10 +10819,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10816,7 +10830,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
@@ -10828,29 +10842,29 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>271</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>82</v>
@@ -10868,13 +10882,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10892,7 +10906,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10901,7 +10915,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10913,10 +10927,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>196</v>
+        <v>497</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10927,24 +10941,24 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -10953,19 +10967,19 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10993,10 +11007,10 @@
         <v>155</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11014,16 +11028,16 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -11032,31 +11046,31 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>529</v>
+        <v>196</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11075,19 +11089,19 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>533</v>
+        <v>276</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11112,13 +11126,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11136,7 +11150,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11154,27 +11168,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11185,7 +11199,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11197,18 +11211,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>271</v>
+        <v>538</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11232,13 +11248,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11256,13 +11272,13 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -11274,27 +11290,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11317,20 +11333,18 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11356,9 +11370,11 @@
       <c r="X74" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Y74" s="2"/>
+      <c r="Y74" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11376,7 +11392,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11394,27 +11410,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11437,18 +11453,20 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11472,13 +11490,11 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11496,7 +11512,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11514,27 +11530,27 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11548,7 +11564,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11557,16 +11573,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11616,7 +11632,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11634,27 +11650,27 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11665,10 +11681,10 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -11677,20 +11693,18 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11738,45 +11752,45 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>582</v>
+        <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11787,7 +11801,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11799,16 +11813,20 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>582</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11856,19 +11874,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11877,10 +11895,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>111</v>
+        <v>589</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11891,21 +11909,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11917,17 +11935,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11976,19 +11992,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -12011,14 +12027,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>588</v>
+        <v>113</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12031,26 +12047,24 @@
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>589</v>
+        <v>115</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12098,7 +12112,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>121</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12122,7 +12136,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12140,26 +12154,26 @@
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>593</v>
+        <v>114</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>594</v>
@@ -12167,8 +12181,12 @@
       <c r="M81" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="N81" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12216,19 +12234,19 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12237,10 +12255,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>598</v>
+        <v>196</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12251,10 +12269,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12277,13 +12295,13 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12334,7 +12352,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12343,7 +12361,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12355,10 +12373,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12369,10 +12387,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12395,20 +12413,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>271</v>
+        <v>598</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N83" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>607</v>
-      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12432,13 +12446,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12456,7 +12470,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12465,7 +12479,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12474,13 +12488,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>530</v>
+        <v>607</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12491,10 +12505,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12505,7 +12519,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12517,19 +12531,19 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12554,13 +12568,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12578,13 +12592,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12596,13 +12610,13 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12613,10 +12627,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12627,7 +12641,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12639,17 +12653,19 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12674,13 +12690,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12698,13 +12714,13 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
@@ -12716,13 +12732,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>615</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>624</v>
+        <v>535</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12733,10 +12749,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12759,7 +12775,7 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>625</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>626</v>
@@ -12768,7 +12784,9 @@
         <v>627</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12816,7 +12834,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12837,10 +12855,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12851,10 +12869,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12865,7 +12883,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12874,10 +12892,10 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>630</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>631</v>
@@ -12885,9 +12903,7 @@
       <c r="M87" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N87" t="s" s="2">
-        <v>633</v>
-      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12936,13 +12952,13 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
@@ -12957,10 +12973,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>634</v>
+        <v>602</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12971,10 +12987,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12997,16 +13013,16 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13056,7 +13072,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13077,10 +13093,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13091,10 +13107,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13108,7 +13124,7 @@
         <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
@@ -13117,20 +13133,18 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>577</v>
+        <v>642</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>643</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O89" t="s" s="2">
         <v>645</v>
       </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13178,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13190,19 +13204,19 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13213,10 +13227,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13227,28 +13241,32 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>582</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>108</v>
+        <v>648</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13296,19 +13314,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>110</v>
+        <v>647</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13317,10 +13335,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>111</v>
+        <v>653</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13331,21 +13349,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13357,17 +13375,15 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13416,19 +13432,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13451,14 +13467,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>588</v>
+        <v>113</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13471,26 +13487,24 @@
         <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>589</v>
+        <v>115</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O92" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13538,7 +13552,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>591</v>
+        <v>121</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13562,7 +13576,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13573,45 +13587,45 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I93" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>271</v>
+        <v>114</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>653</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>654</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>655</v>
+        <v>117</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>656</v>
+        <v>234</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13636,13 +13650,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13660,34 +13674,34 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>652</v>
+        <v>596</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>365</v>
+        <v>196</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>82</v>
@@ -13695,10 +13709,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13706,7 +13720,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>93</v>
@@ -13721,19 +13735,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13761,10 +13775,10 @@
         <v>155</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>663</v>
+        <v>365</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>664</v>
+        <v>366</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13782,16 +13796,16 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13800,27 +13814,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>456</v>
+        <v>369</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13840,22 +13854,22 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>271</v>
+        <v>664</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>515</v>
+        <v>456</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13883,10 +13897,10 @@
         <v>155</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>516</v>
+        <v>668</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>517</v>
+        <v>669</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13904,7 +13918,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13913,7 +13927,7 @@
         <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13922,19 +13936,19 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>671</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>196</v>
+        <v>461</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>519</v>
+        <v>462</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
     </row>
     <row r="96" hidden="true">
@@ -13946,17 +13960,17 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -13965,19 +13979,19 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>522</v>
+        <v>673</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>523</v>
+        <v>674</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>524</v>
+        <v>675</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14005,10 +14019,10 @@
         <v>155</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14032,10 +14046,10 @@
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>105</v>
@@ -14044,31 +14058,31 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>529</v>
+        <v>196</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14087,19 +14101,19 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>674</v>
+        <v>527</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>675</v>
+        <v>528</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>580</v>
+        <v>529</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14124,13 +14138,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14148,7 +14162,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14166,23 +14180,145 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>583</v>
+        <v>534</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>584</v>
+        <v>535</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP97">
+  <autoFilter ref="A1:AP98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14192,7 +14328,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1399,7 +1399,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2472,7 +2472,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
